--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130375737</v>
       </c>
       <c r="B3" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130375736</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130375737</v>
       </c>
       <c r="B3" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130375737</v>
       </c>
       <c r="B3" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130375737</v>
       </c>
       <c r="B3" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130375736</v>
       </c>
       <c r="B2" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130375737</v>
       </c>
       <c r="B3" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130375737</v>
       </c>
       <c r="B3" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130375736</v>
       </c>
       <c r="B2" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130375737</v>
       </c>
       <c r="B3" t="n">
-        <v>93047</v>
+        <v>93060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130375736</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130375737</v>
       </c>
       <c r="B3" t="n">
-        <v>93060</v>
+        <v>93061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130375736</v>
       </c>
       <c r="B2" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130375737</v>
       </c>
       <c r="B3" t="n">
-        <v>93061</v>
+        <v>93062</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130375737</v>
       </c>
       <c r="B3" t="n">
-        <v>93062</v>
+        <v>93071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>132050115</v>
       </c>
       <c r="B4" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>132050110</v>
       </c>
       <c r="B5" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>132050114</v>
       </c>
       <c r="B7" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>132050111</v>
       </c>
       <c r="B8" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>132050113</v>
       </c>
       <c r="B9" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>132050115</v>
       </c>
       <c r="B4" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>132050110</v>
       </c>
       <c r="B5" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>132050109</v>
       </c>
       <c r="B6" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>132050114</v>
       </c>
       <c r="B7" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>132050111</v>
       </c>
       <c r="B8" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>132050113</v>
       </c>
       <c r="B9" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>132050115</v>
       </c>
       <c r="B4" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>132050110</v>
       </c>
       <c r="B5" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>132050109</v>
       </c>
       <c r="B6" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>132050114</v>
       </c>
       <c r="B7" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>132050111</v>
       </c>
       <c r="B8" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>132050113</v>
       </c>
       <c r="B9" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>132050115</v>
       </c>
       <c r="B4" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>132050110</v>
       </c>
       <c r="B5" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>132050114</v>
       </c>
       <c r="B7" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>132050111</v>
       </c>
       <c r="B8" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>132050113</v>
       </c>
       <c r="B9" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 61168-2025 artfynd.xlsx
+++ b/artfynd/A 61168-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130375736</v>
+        <v>130375737</v>
       </c>
       <c r="B2" t="n">
-        <v>58023</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342028</v>
+        <v>342407</v>
       </c>
       <c r="R2" t="n">
-        <v>6567014</v>
+        <v>6566664</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130375737</v>
+        <v>132050110</v>
       </c>
       <c r="B3" t="n">
-        <v>93071</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>342407</v>
+        <v>342315</v>
       </c>
       <c r="R3" t="n">
-        <v>6566664</v>
+        <v>6567248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,14 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132050115</v>
+        <v>132050111</v>
       </c>
       <c r="B4" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>342339</v>
+        <v>342313</v>
       </c>
       <c r="R4" t="n">
-        <v>6567210</v>
+        <v>6567176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132050110</v>
+        <v>132050112</v>
       </c>
       <c r="B5" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>342315</v>
+        <v>342347</v>
       </c>
       <c r="R5" t="n">
-        <v>6567248</v>
+        <v>6566990</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,53 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132050109</v>
+        <v>132050113</v>
       </c>
       <c r="B6" t="n">
-        <v>57141</v>
+        <v>93271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Orremossen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>342334</v>
+        <v>342445</v>
       </c>
       <c r="R6" t="n">
-        <v>6567254</v>
+        <v>6566818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,11 +1163,11 @@
         <v>132050114</v>
       </c>
       <c r="B7" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1270,14 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132050111</v>
+        <v>132050115</v>
       </c>
       <c r="B8" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1305,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>342313</v>
+        <v>342339</v>
       </c>
       <c r="R8" t="n">
-        <v>6567176</v>
+        <v>6567210</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132050113</v>
+        <v>132214415</v>
       </c>
       <c r="B9" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1398,14 +1385,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orremossen, Dls</t>
+          <t>Orremossen, Orremossen, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>342445</v>
+        <v>342402</v>
       </c>
       <c r="R9" t="n">
-        <v>6566818</v>
+        <v>6567032</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1432,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,6 +1448,538 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115245677</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bremossen, Bremossen, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>342331</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6567293</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning i lämplig biotop för spelplats</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132044408</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bremossen, Bremossen, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>342336</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6567311</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132050109</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Orremossen, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>342334</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6567254</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130375736</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Orremossen, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>342028</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6567014</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132214766</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Orremossen, Orremossen, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>342402</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6567032</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
